--- a/RSI Modular - copia/tabla_maestra_ILF.xlsx
+++ b/RSI Modular - copia/tabla_maestra_ILF.xlsx
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="I4" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="J4" t="n">
-        <v>4.95</v>
+        <v>4.58</v>
       </c>
       <c r="K4" t="n">
-        <v>7.84</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="5">
@@ -790,28 +790,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H10" t="n">
         <v>0.04</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.25</v>
-      </c>
       <c r="I10" t="n">
-        <v>-0.86</v>
+        <v>-1.17</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.23</v>
+        <v>-2.97</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.79</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="11">
@@ -906,7 +906,7 @@
         <v>0.77</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.36</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="14">
@@ -1133,28 +1133,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>52.9</v>
       </c>
       <c r="G4" t="n">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="H4" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="I4" t="n">
         <v>62.5</v>
       </c>
-      <c r="I4" t="n">
-        <v>63.8</v>
-      </c>
       <c r="J4" t="n">
-        <v>67.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K4" t="n">
-        <v>60.5</v>
+        <v>59.1</v>
       </c>
     </row>
     <row r="5">
@@ -1337,28 +1337,28 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="n">
-        <v>53.6</v>
+        <v>51.9</v>
       </c>
       <c r="F10" t="n">
-        <v>46.4</v>
+        <v>44.4</v>
       </c>
       <c r="G10" t="n">
-        <v>57.1</v>
+        <v>55.6</v>
       </c>
       <c r="H10" t="n">
-        <v>50</v>
+        <v>48.1</v>
       </c>
       <c r="I10" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="J10" t="n">
-        <v>32.1</v>
+        <v>29.6</v>
       </c>
       <c r="K10" t="n">
-        <v>44.4</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="11">
@@ -1453,7 +1453,7 @@
         <v>50</v>
       </c>
       <c r="K13" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -1886,15 +1886,23 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>**</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
